--- a/raw/Timetable_2026Autumn_2026IE.xlsx
+++ b/raw/Timetable_2026Autumn_2026IE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C80D214-65ED-4192-9F85-EC9943380C7A}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E124CC-1DB1-4794-ACBD-A26905E1B2E9}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,7 +186,7 @@
     <t>Introduction to Professional Field</t>
   </si>
   <si>
-    <t>GGG</t>
+    <t>XIE Pengtao</t>
   </si>
   <si>
     <t>8       Sep.</t>
@@ -946,31 +946,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1000,7 +976,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1016,6 +995,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1366,81 +1366,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45" t="s">
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45" t="s">
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45" t="s">
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="46" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45" t="s">
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45" t="s">
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="34">
+      <c r="A4" s="37">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1494,7 +1494,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="34"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -1554,7 +1554,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
@@ -1614,7 +1614,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="34"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
@@ -1660,7 +1660,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="34"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="6" t="s">
         <v>37</v>
       </c>
@@ -1706,7 +1706,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="34"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="6" t="s">
         <v>39</v>
       </c>
@@ -1756,7 +1756,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="34"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
@@ -1800,7 +1800,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="38">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1862,7 +1862,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="35"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="11" t="s">
         <v>50</v>
       </c>
@@ -1920,7 +1920,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="35"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="11" t="s">
         <v>51</v>
       </c>
@@ -1990,7 +1990,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="35"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="11" t="s">
         <v>55</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="35"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="11" t="s">
         <v>56</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="35"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="11" t="s">
         <v>57</v>
       </c>
@@ -2090,7 +2090,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="35"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="11" t="s">
         <v>58</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="37">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2162,7 +2162,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="34"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
@@ -2205,7 +2205,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="34"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
@@ -2260,7 +2260,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="34"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -2291,7 +2291,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="34"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
@@ -2320,7 +2320,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="34"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
@@ -2347,7 +2347,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="34"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="15" t="s">
         <v>65</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="U24" s="18"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="38">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -2419,7 +2419,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="35"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="11" t="s">
         <v>67</v>
       </c>
@@ -2462,7 +2462,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="35"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="11" t="s">
         <v>68</v>
       </c>
@@ -2517,7 +2517,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="35"/>
+      <c r="A28" s="38"/>
       <c r="B28" s="11" t="s">
         <v>69</v>
       </c>
@@ -2548,90 +2548,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="35"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="38"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="30"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="35"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="19" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="41"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="33"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="35"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="44"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="34">
+      <c r="A32" s="37">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2676,7 +2676,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="34"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="6" t="s">
         <v>75</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="34"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="6" t="s">
         <v>76</v>
       </c>
@@ -2762,117 +2762,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="34"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-      <c r="T35" s="37"/>
-      <c r="U35" s="38"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="30"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="34"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="41"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="33"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="34"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="21" t="s">
         <v>79</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="41"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="33"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="34"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="21" t="s">
         <v>80</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="40"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="40"/>
-      <c r="U38" s="41"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="33"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="35">
+      <c r="A39" s="38">
         <v>6</v>
       </c>
       <c r="B39" s="21" t="s">
@@ -2881,81 +2881,81 @@
       <c r="C39" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="40"/>
-      <c r="U39" s="41"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="33"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="35"/>
+      <c r="A40" s="38"/>
       <c r="B40" s="21" t="s">
         <v>82</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="41"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="33"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="35"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="21" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="44"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="36"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="35"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="22" t="s">
         <v>84</v>
       </c>
@@ -2998,7 +2998,7 @@
       <c r="U42" s="14"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="35"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="22" t="s">
         <v>85</v>
       </c>
@@ -3039,7 +3039,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="35"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="23" t="s">
         <v>86</v>
       </c>
@@ -3066,7 +3066,7 @@
       <c r="U44" s="18"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="35"/>
+      <c r="A45" s="38"/>
       <c r="B45" s="22" t="s">
         <v>87</v>
       </c>
@@ -3093,7 +3093,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="34">
+      <c r="A46" s="37">
         <v>7</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -3138,7 +3138,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="34"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="24" t="s">
         <v>89</v>
       </c>
@@ -3181,7 +3181,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="34"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="24" t="s">
         <v>90</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="34"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="24" t="s">
         <v>91</v>
       </c>
@@ -3267,7 +3267,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="34"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="24" t="s">
         <v>93</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="34"/>
+      <c r="A51" s="37"/>
       <c r="B51" s="24" t="s">
         <v>95</v>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="34"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="24" t="s">
         <v>96</v>
       </c>
@@ -3370,7 +3370,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="35">
+      <c r="A53" s="38">
         <v>8</v>
       </c>
       <c r="B53" s="22" t="s">
@@ -3415,7 +3415,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="35"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="22" t="s">
         <v>98</v>
       </c>
@@ -3458,7 +3458,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="35"/>
+      <c r="A55" s="38"/>
       <c r="B55" s="22" t="s">
         <v>99</v>
       </c>
@@ -3513,7 +3513,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="35"/>
+      <c r="A56" s="38"/>
       <c r="B56" s="22" t="s">
         <v>100</v>
       </c>
@@ -3556,7 +3556,7 @@
       <c r="U56" s="14"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="35"/>
+      <c r="A57" s="38"/>
       <c r="B57" s="22" t="s">
         <v>101</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="35"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="22" t="s">
         <v>102</v>
       </c>
@@ -3634,7 +3634,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="35"/>
+      <c r="A59" s="38"/>
       <c r="B59" s="22" t="s">
         <v>103</v>
       </c>
@@ -3661,7 +3661,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="34">
+      <c r="A60" s="37">
         <v>9</v>
       </c>
       <c r="B60" s="24" t="s">
@@ -3706,7 +3706,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="34"/>
+      <c r="A61" s="37"/>
       <c r="B61" s="24" t="s">
         <v>105</v>
       </c>
@@ -3749,7 +3749,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="34"/>
+      <c r="A62" s="37"/>
       <c r="B62" s="24" t="s">
         <v>106</v>
       </c>
@@ -3804,7 +3804,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="34"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="24" t="s">
         <v>107</v>
       </c>
@@ -3847,7 +3847,7 @@
       <c r="U63" s="25"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="34"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="24" t="s">
         <v>108</v>
       </c>
@@ -3890,7 +3890,7 @@
       <c r="U64" s="25"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="34"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="24" t="s">
         <v>109</v>
       </c>
@@ -3925,7 +3925,7 @@
       <c r="U65" s="25"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="34"/>
+      <c r="A66" s="37"/>
       <c r="B66" s="24" t="s">
         <v>110</v>
       </c>
@@ -3952,7 +3952,7 @@
       <c r="U66" s="25"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="35">
+      <c r="A67" s="38">
         <v>10</v>
       </c>
       <c r="B67" s="22" t="s">
@@ -3997,7 +3997,7 @@
       <c r="U67" s="26"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="35"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="22" t="s">
         <v>112</v>
       </c>
@@ -4040,7 +4040,7 @@
       <c r="U68" s="26"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="35"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="22" t="s">
         <v>113</v>
       </c>
@@ -4083,7 +4083,7 @@
       <c r="U69" s="26"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="35"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="22" t="s">
         <v>114</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="U70" s="26"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="35"/>
+      <c r="A71" s="38"/>
       <c r="B71" s="22" t="s">
         <v>115</v>
       </c>
@@ -4169,7 +4169,7 @@
       <c r="U71" s="26"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="35"/>
+      <c r="A72" s="38"/>
       <c r="B72" s="22" t="s">
         <v>116</v>
       </c>
@@ -4196,7 +4196,7 @@
       <c r="U72" s="26"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="35"/>
+      <c r="A73" s="38"/>
       <c r="B73" s="22" t="s">
         <v>117</v>
       </c>
@@ -4223,7 +4223,7 @@
       <c r="U73" s="26"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="34">
+      <c r="A74" s="37">
         <v>11</v>
       </c>
       <c r="B74" s="24" t="s">
@@ -4268,7 +4268,7 @@
       <c r="U74" s="25"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="34"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="24" t="s">
         <v>119</v>
       </c>
@@ -4311,7 +4311,7 @@
       <c r="U75" s="25"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="34"/>
+      <c r="A76" s="37"/>
       <c r="B76" s="24" t="s">
         <v>120</v>
       </c>
@@ -4366,7 +4366,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="34"/>
+      <c r="A77" s="37"/>
       <c r="B77" s="24" t="s">
         <v>121</v>
       </c>
@@ -4409,7 +4409,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="34"/>
+      <c r="A78" s="37"/>
       <c r="B78" s="24" t="s">
         <v>122</v>
       </c>
@@ -4452,7 +4452,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="34"/>
+      <c r="A79" s="37"/>
       <c r="B79" s="24" t="s">
         <v>123</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="34"/>
+      <c r="A80" s="37"/>
       <c r="B80" s="24" t="s">
         <v>124</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="35">
+      <c r="A81" s="38">
         <v>12</v>
       </c>
       <c r="B81" s="22" t="s">
@@ -4551,7 +4551,7 @@
       <c r="U81" s="14"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="35"/>
+      <c r="A82" s="38"/>
       <c r="B82" s="22" t="s">
         <v>126</v>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="U82" s="14"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="35"/>
+      <c r="A83" s="38"/>
       <c r="B83" s="22" t="s">
         <v>127</v>
       </c>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="35"/>
+      <c r="A84" s="38"/>
       <c r="B84" s="22" t="s">
         <v>130</v>
       </c>
@@ -4692,7 +4692,7 @@
       <c r="U84" s="14"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="35"/>
+      <c r="A85" s="38"/>
       <c r="B85" s="22" t="s">
         <v>131</v>
       </c>
@@ -4735,7 +4735,7 @@
       <c r="U85" s="14"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="35"/>
+      <c r="A86" s="38"/>
       <c r="B86" s="22" t="s">
         <v>132</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="U86" s="14"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="35"/>
+      <c r="A87" s="38"/>
       <c r="B87" s="22" t="s">
         <v>133</v>
       </c>
@@ -4797,7 +4797,7 @@
       <c r="U87" s="14"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="34">
+      <c r="A88" s="37">
         <v>13</v>
       </c>
       <c r="B88" s="24" t="s">
@@ -4842,7 +4842,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="34"/>
+      <c r="A89" s="37"/>
       <c r="B89" s="24" t="s">
         <v>135</v>
       </c>
@@ -4885,7 +4885,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="34"/>
+      <c r="A90" s="37"/>
       <c r="B90" s="24" t="s">
         <v>136</v>
       </c>
@@ -4940,7 +4940,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="34"/>
+      <c r="A91" s="37"/>
       <c r="B91" s="24" t="s">
         <v>137</v>
       </c>
@@ -4983,7 +4983,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="34"/>
+      <c r="A92" s="37"/>
       <c r="B92" s="24" t="s">
         <v>138</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="34"/>
+      <c r="A93" s="37"/>
       <c r="B93" s="24" t="s">
         <v>139</v>
       </c>
@@ -5061,7 +5061,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="34"/>
+      <c r="A94" s="37"/>
       <c r="B94" s="24" t="s">
         <v>140</v>
       </c>
@@ -5088,7 +5088,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="35">
+      <c r="A95" s="38">
         <v>14</v>
       </c>
       <c r="B95" s="22" t="s">
@@ -5133,7 +5133,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="35"/>
+      <c r="A96" s="38"/>
       <c r="B96" s="22" t="s">
         <v>142</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="35"/>
+      <c r="A97" s="38"/>
       <c r="B97" s="22" t="s">
         <v>143</v>
       </c>
@@ -5231,7 +5231,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="35"/>
+      <c r="A98" s="38"/>
       <c r="B98" s="22" t="s">
         <v>144</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="35"/>
+      <c r="A99" s="38"/>
       <c r="B99" s="22" t="s">
         <v>145</v>
       </c>
@@ -5317,7 +5317,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="35"/>
+      <c r="A100" s="38"/>
       <c r="B100" s="22" t="s">
         <v>146</v>
       </c>
@@ -5344,7 +5344,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="35"/>
+      <c r="A101" s="38"/>
       <c r="B101" s="22" t="s">
         <v>147</v>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="34">
+      <c r="A102" s="37">
         <v>15</v>
       </c>
       <c r="B102" s="24" t="s">
@@ -5416,7 +5416,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="34"/>
+      <c r="A103" s="37"/>
       <c r="B103" s="24" t="s">
         <v>149</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="34"/>
+      <c r="A104" s="37"/>
       <c r="B104" s="24" t="s">
         <v>150</v>
       </c>
@@ -5514,7 +5514,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="34"/>
+      <c r="A105" s="37"/>
       <c r="B105" s="24" t="s">
         <v>151</v>
       </c>
@@ -5557,7 +5557,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="34"/>
+      <c r="A106" s="37"/>
       <c r="B106" s="24" t="s">
         <v>152</v>
       </c>
@@ -5600,7 +5600,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="34"/>
+      <c r="A107" s="37"/>
       <c r="B107" s="24" t="s">
         <v>153</v>
       </c>
@@ -5635,7 +5635,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="34"/>
+      <c r="A108" s="37"/>
       <c r="B108" s="24" t="s">
         <v>154</v>
       </c>
@@ -5662,7 +5662,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="35">
+      <c r="A109" s="38">
         <v>16</v>
       </c>
       <c r="B109" s="22" t="s">
@@ -5707,7 +5707,7 @@
       <c r="U109" s="26"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="35"/>
+      <c r="A110" s="38"/>
       <c r="B110" s="22" t="s">
         <v>156</v>
       </c>
@@ -5750,7 +5750,7 @@
       <c r="U110" s="26"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="35"/>
+      <c r="A111" s="38"/>
       <c r="B111" s="22" t="s">
         <v>157</v>
       </c>
@@ -5805,7 +5805,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="35"/>
+      <c r="A112" s="38"/>
       <c r="B112" s="22" t="s">
         <v>158</v>
       </c>
@@ -5848,7 +5848,7 @@
       <c r="U112" s="26"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="35"/>
+      <c r="A113" s="38"/>
       <c r="B113" s="22" t="s">
         <v>159</v>
       </c>
@@ -5891,7 +5891,7 @@
       <c r="U113" s="26"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="35"/>
+      <c r="A114" s="38"/>
       <c r="B114" s="22" t="s">
         <v>160</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="U114" s="26"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="35"/>
+      <c r="A115" s="38"/>
       <c r="B115" s="22" t="s">
         <v>161</v>
       </c>
@@ -5945,7 +5945,7 @@
       <c r="U115" s="26"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="34">
+      <c r="A116" s="37">
         <v>17</v>
       </c>
       <c r="B116" s="24" t="s">
@@ -5988,7 +5988,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="34"/>
+      <c r="A117" s="37"/>
       <c r="B117" s="24" t="s">
         <v>163</v>
       </c>
@@ -6017,7 +6017,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="34"/>
+      <c r="A118" s="37"/>
       <c r="B118" s="24" t="s">
         <v>164</v>
       </c>
@@ -6058,7 +6058,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="34"/>
+      <c r="A119" s="37"/>
       <c r="B119" s="24" t="s">
         <v>165</v>
       </c>
@@ -6099,7 +6099,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="34"/>
+      <c r="A120" s="37"/>
       <c r="B120" s="24" t="s">
         <v>166</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="34"/>
+      <c r="A121" s="37"/>
       <c r="B121" s="24" t="s">
         <v>167</v>
       </c>
@@ -6169,7 +6169,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="34"/>
+      <c r="A122" s="37"/>
       <c r="B122" s="24" t="s">
         <v>168</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="35">
+      <c r="A123" s="38">
         <v>18</v>
       </c>
       <c r="B123" s="22" t="s">
@@ -6205,191 +6205,191 @@
       <c r="C123" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="27" t="s">
+      <c r="D123" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="E123" s="28"/>
-      <c r="F123" s="28"/>
-      <c r="G123" s="28"/>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="28"/>
-      <c r="K123" s="28"/>
-      <c r="L123" s="28"/>
-      <c r="M123" s="28"/>
-      <c r="N123" s="28"/>
-      <c r="O123" s="28"/>
-      <c r="P123" s="28"/>
-      <c r="Q123" s="28"/>
-      <c r="R123" s="28"/>
-      <c r="S123" s="28"/>
-      <c r="T123" s="28"/>
-      <c r="U123" s="29"/>
+      <c r="E123" s="45"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="45"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="45"/>
+      <c r="J123" s="45"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="45"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="45"/>
+      <c r="O123" s="45"/>
+      <c r="P123" s="45"/>
+      <c r="Q123" s="45"/>
+      <c r="R123" s="45"/>
+      <c r="S123" s="45"/>
+      <c r="T123" s="45"/>
+      <c r="U123" s="46"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="35"/>
+      <c r="A124" s="38"/>
       <c r="B124" s="22" t="s">
         <v>171</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="30"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="30"/>
-      <c r="H124" s="30"/>
-      <c r="I124" s="30"/>
-      <c r="J124" s="30"/>
-      <c r="K124" s="30"/>
-      <c r="L124" s="30"/>
-      <c r="M124" s="30"/>
-      <c r="N124" s="30"/>
-      <c r="O124" s="30"/>
-      <c r="P124" s="30"/>
-      <c r="Q124" s="30"/>
-      <c r="R124" s="30"/>
-      <c r="S124" s="30"/>
-      <c r="T124" s="30"/>
-      <c r="U124" s="31"/>
+      <c r="D124" s="47"/>
+      <c r="E124" s="47"/>
+      <c r="F124" s="47"/>
+      <c r="G124" s="47"/>
+      <c r="H124" s="47"/>
+      <c r="I124" s="47"/>
+      <c r="J124" s="47"/>
+      <c r="K124" s="47"/>
+      <c r="L124" s="47"/>
+      <c r="M124" s="47"/>
+      <c r="N124" s="47"/>
+      <c r="O124" s="47"/>
+      <c r="P124" s="47"/>
+      <c r="Q124" s="47"/>
+      <c r="R124" s="47"/>
+      <c r="S124" s="47"/>
+      <c r="T124" s="47"/>
+      <c r="U124" s="48"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="35"/>
+      <c r="A125" s="38"/>
       <c r="B125" s="22" t="s">
         <v>172</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D125" s="30"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="30"/>
-      <c r="H125" s="30"/>
-      <c r="I125" s="30"/>
-      <c r="J125" s="30"/>
-      <c r="K125" s="30"/>
-      <c r="L125" s="30"/>
-      <c r="M125" s="30"/>
-      <c r="N125" s="30"/>
-      <c r="O125" s="30"/>
-      <c r="P125" s="30"/>
-      <c r="Q125" s="30"/>
-      <c r="R125" s="30"/>
-      <c r="S125" s="30"/>
-      <c r="T125" s="30"/>
-      <c r="U125" s="31"/>
+      <c r="D125" s="47"/>
+      <c r="E125" s="47"/>
+      <c r="F125" s="47"/>
+      <c r="G125" s="47"/>
+      <c r="H125" s="47"/>
+      <c r="I125" s="47"/>
+      <c r="J125" s="47"/>
+      <c r="K125" s="47"/>
+      <c r="L125" s="47"/>
+      <c r="M125" s="47"/>
+      <c r="N125" s="47"/>
+      <c r="O125" s="47"/>
+      <c r="P125" s="47"/>
+      <c r="Q125" s="47"/>
+      <c r="R125" s="47"/>
+      <c r="S125" s="47"/>
+      <c r="T125" s="47"/>
+      <c r="U125" s="48"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="35"/>
+      <c r="A126" s="38"/>
       <c r="B126" s="22" t="s">
         <v>173</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D126" s="30"/>
-      <c r="E126" s="30"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="30"/>
-      <c r="H126" s="30"/>
-      <c r="I126" s="30"/>
-      <c r="J126" s="30"/>
-      <c r="K126" s="30"/>
-      <c r="L126" s="30"/>
-      <c r="M126" s="30"/>
-      <c r="N126" s="30"/>
-      <c r="O126" s="30"/>
-      <c r="P126" s="30"/>
-      <c r="Q126" s="30"/>
-      <c r="R126" s="30"/>
-      <c r="S126" s="30"/>
-      <c r="T126" s="30"/>
-      <c r="U126" s="31"/>
+      <c r="D126" s="47"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="47"/>
+      <c r="G126" s="47"/>
+      <c r="H126" s="47"/>
+      <c r="I126" s="47"/>
+      <c r="J126" s="47"/>
+      <c r="K126" s="47"/>
+      <c r="L126" s="47"/>
+      <c r="M126" s="47"/>
+      <c r="N126" s="47"/>
+      <c r="O126" s="47"/>
+      <c r="P126" s="47"/>
+      <c r="Q126" s="47"/>
+      <c r="R126" s="47"/>
+      <c r="S126" s="47"/>
+      <c r="T126" s="47"/>
+      <c r="U126" s="48"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="35"/>
+      <c r="A127" s="38"/>
       <c r="B127" s="21" t="s">
         <v>174</v>
       </c>
       <c r="C127" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="30"/>
-      <c r="E127" s="30"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="30"/>
-      <c r="H127" s="30"/>
-      <c r="I127" s="30"/>
-      <c r="J127" s="30"/>
-      <c r="K127" s="30"/>
-      <c r="L127" s="30"/>
-      <c r="M127" s="30"/>
-      <c r="N127" s="30"/>
-      <c r="O127" s="30"/>
-      <c r="P127" s="30"/>
-      <c r="Q127" s="30"/>
-      <c r="R127" s="30"/>
-      <c r="S127" s="30"/>
-      <c r="T127" s="30"/>
-      <c r="U127" s="31"/>
+      <c r="D127" s="47"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47"/>
+      <c r="G127" s="47"/>
+      <c r="H127" s="47"/>
+      <c r="I127" s="47"/>
+      <c r="J127" s="47"/>
+      <c r="K127" s="47"/>
+      <c r="L127" s="47"/>
+      <c r="M127" s="47"/>
+      <c r="N127" s="47"/>
+      <c r="O127" s="47"/>
+      <c r="P127" s="47"/>
+      <c r="Q127" s="47"/>
+      <c r="R127" s="47"/>
+      <c r="S127" s="47"/>
+      <c r="T127" s="47"/>
+      <c r="U127" s="48"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="35"/>
+      <c r="A128" s="38"/>
       <c r="B128" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="30"/>
-      <c r="H128" s="30"/>
-      <c r="I128" s="30"/>
-      <c r="J128" s="30"/>
-      <c r="K128" s="30"/>
-      <c r="L128" s="30"/>
-      <c r="M128" s="30"/>
-      <c r="N128" s="30"/>
-      <c r="O128" s="30"/>
-      <c r="P128" s="30"/>
-      <c r="Q128" s="30"/>
-      <c r="R128" s="30"/>
-      <c r="S128" s="30"/>
-      <c r="T128" s="30"/>
-      <c r="U128" s="31"/>
+      <c r="D128" s="47"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="47"/>
+      <c r="G128" s="47"/>
+      <c r="H128" s="47"/>
+      <c r="I128" s="47"/>
+      <c r="J128" s="47"/>
+      <c r="K128" s="47"/>
+      <c r="L128" s="47"/>
+      <c r="M128" s="47"/>
+      <c r="N128" s="47"/>
+      <c r="O128" s="47"/>
+      <c r="P128" s="47"/>
+      <c r="Q128" s="47"/>
+      <c r="R128" s="47"/>
+      <c r="S128" s="47"/>
+      <c r="T128" s="47"/>
+      <c r="U128" s="48"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="35"/>
+      <c r="A129" s="38"/>
       <c r="B129" s="22" t="s">
         <v>176</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D129" s="30"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="30"/>
-      <c r="H129" s="30"/>
-      <c r="I129" s="30"/>
-      <c r="J129" s="30"/>
-      <c r="K129" s="30"/>
-      <c r="L129" s="30"/>
-      <c r="M129" s="30"/>
-      <c r="N129" s="30"/>
-      <c r="O129" s="30"/>
-      <c r="P129" s="30"/>
-      <c r="Q129" s="30"/>
-      <c r="R129" s="30"/>
-      <c r="S129" s="30"/>
-      <c r="T129" s="30"/>
-      <c r="U129" s="31"/>
+      <c r="D129" s="47"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="47"/>
+      <c r="G129" s="47"/>
+      <c r="H129" s="47"/>
+      <c r="I129" s="47"/>
+      <c r="J129" s="47"/>
+      <c r="K129" s="47"/>
+      <c r="L129" s="47"/>
+      <c r="M129" s="47"/>
+      <c r="N129" s="47"/>
+      <c r="O129" s="47"/>
+      <c r="P129" s="47"/>
+      <c r="Q129" s="47"/>
+      <c r="R129" s="47"/>
+      <c r="S129" s="47"/>
+      <c r="T129" s="47"/>
+      <c r="U129" s="48"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="34">
+      <c r="A130" s="37">
         <v>19</v>
       </c>
       <c r="B130" s="24" t="s">
@@ -6398,186 +6398,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="30"/>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="30"/>
-      <c r="H130" s="30"/>
-      <c r="I130" s="30"/>
-      <c r="J130" s="30"/>
-      <c r="K130" s="30"/>
-      <c r="L130" s="30"/>
-      <c r="M130" s="30"/>
-      <c r="N130" s="30"/>
-      <c r="O130" s="30"/>
-      <c r="P130" s="30"/>
-      <c r="Q130" s="30"/>
-      <c r="R130" s="30"/>
-      <c r="S130" s="30"/>
-      <c r="T130" s="30"/>
-      <c r="U130" s="31"/>
+      <c r="D130" s="47"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="47"/>
+      <c r="G130" s="47"/>
+      <c r="H130" s="47"/>
+      <c r="I130" s="47"/>
+      <c r="J130" s="47"/>
+      <c r="K130" s="47"/>
+      <c r="L130" s="47"/>
+      <c r="M130" s="47"/>
+      <c r="N130" s="47"/>
+      <c r="O130" s="47"/>
+      <c r="P130" s="47"/>
+      <c r="Q130" s="47"/>
+      <c r="R130" s="47"/>
+      <c r="S130" s="47"/>
+      <c r="T130" s="47"/>
+      <c r="U130" s="48"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="34"/>
+      <c r="A131" s="37"/>
       <c r="B131" s="24" t="s">
         <v>178</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="30"/>
-      <c r="E131" s="30"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="30"/>
-      <c r="H131" s="30"/>
-      <c r="I131" s="30"/>
-      <c r="J131" s="30"/>
-      <c r="K131" s="30"/>
-      <c r="L131" s="30"/>
-      <c r="M131" s="30"/>
-      <c r="N131" s="30"/>
-      <c r="O131" s="30"/>
-      <c r="P131" s="30"/>
-      <c r="Q131" s="30"/>
-      <c r="R131" s="30"/>
-      <c r="S131" s="30"/>
-      <c r="T131" s="30"/>
-      <c r="U131" s="31"/>
+      <c r="D131" s="47"/>
+      <c r="E131" s="47"/>
+      <c r="F131" s="47"/>
+      <c r="G131" s="47"/>
+      <c r="H131" s="47"/>
+      <c r="I131" s="47"/>
+      <c r="J131" s="47"/>
+      <c r="K131" s="47"/>
+      <c r="L131" s="47"/>
+      <c r="M131" s="47"/>
+      <c r="N131" s="47"/>
+      <c r="O131" s="47"/>
+      <c r="P131" s="47"/>
+      <c r="Q131" s="47"/>
+      <c r="R131" s="47"/>
+      <c r="S131" s="47"/>
+      <c r="T131" s="47"/>
+      <c r="U131" s="48"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="34"/>
+      <c r="A132" s="37"/>
       <c r="B132" s="24" t="s">
         <v>179</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D132" s="30"/>
-      <c r="E132" s="30"/>
-      <c r="F132" s="30"/>
-      <c r="G132" s="30"/>
-      <c r="H132" s="30"/>
-      <c r="I132" s="30"/>
-      <c r="J132" s="30"/>
-      <c r="K132" s="30"/>
-      <c r="L132" s="30"/>
-      <c r="M132" s="30"/>
-      <c r="N132" s="30"/>
-      <c r="O132" s="30"/>
-      <c r="P132" s="30"/>
-      <c r="Q132" s="30"/>
-      <c r="R132" s="30"/>
-      <c r="S132" s="30"/>
-      <c r="T132" s="30"/>
-      <c r="U132" s="31"/>
+      <c r="D132" s="47"/>
+      <c r="E132" s="47"/>
+      <c r="F132" s="47"/>
+      <c r="G132" s="47"/>
+      <c r="H132" s="47"/>
+      <c r="I132" s="47"/>
+      <c r="J132" s="47"/>
+      <c r="K132" s="47"/>
+      <c r="L132" s="47"/>
+      <c r="M132" s="47"/>
+      <c r="N132" s="47"/>
+      <c r="O132" s="47"/>
+      <c r="P132" s="47"/>
+      <c r="Q132" s="47"/>
+      <c r="R132" s="47"/>
+      <c r="S132" s="47"/>
+      <c r="T132" s="47"/>
+      <c r="U132" s="48"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="34"/>
+      <c r="A133" s="37"/>
       <c r="B133" s="24" t="s">
         <v>180</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D133" s="30"/>
-      <c r="E133" s="30"/>
-      <c r="F133" s="30"/>
-      <c r="G133" s="30"/>
-      <c r="H133" s="30"/>
-      <c r="I133" s="30"/>
-      <c r="J133" s="30"/>
-      <c r="K133" s="30"/>
-      <c r="L133" s="30"/>
-      <c r="M133" s="30"/>
-      <c r="N133" s="30"/>
-      <c r="O133" s="30"/>
-      <c r="P133" s="30"/>
-      <c r="Q133" s="30"/>
-      <c r="R133" s="30"/>
-      <c r="S133" s="30"/>
-      <c r="T133" s="30"/>
-      <c r="U133" s="31"/>
+      <c r="D133" s="47"/>
+      <c r="E133" s="47"/>
+      <c r="F133" s="47"/>
+      <c r="G133" s="47"/>
+      <c r="H133" s="47"/>
+      <c r="I133" s="47"/>
+      <c r="J133" s="47"/>
+      <c r="K133" s="47"/>
+      <c r="L133" s="47"/>
+      <c r="M133" s="47"/>
+      <c r="N133" s="47"/>
+      <c r="O133" s="47"/>
+      <c r="P133" s="47"/>
+      <c r="Q133" s="47"/>
+      <c r="R133" s="47"/>
+      <c r="S133" s="47"/>
+      <c r="T133" s="47"/>
+      <c r="U133" s="48"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="34"/>
+      <c r="A134" s="37"/>
       <c r="B134" s="24" t="s">
         <v>181</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="30"/>
-      <c r="E134" s="30"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="30"/>
-      <c r="H134" s="30"/>
-      <c r="I134" s="30"/>
-      <c r="J134" s="30"/>
-      <c r="K134" s="30"/>
-      <c r="L134" s="30"/>
-      <c r="M134" s="30"/>
-      <c r="N134" s="30"/>
-      <c r="O134" s="30"/>
-      <c r="P134" s="30"/>
-      <c r="Q134" s="30"/>
-      <c r="R134" s="30"/>
-      <c r="S134" s="30"/>
-      <c r="T134" s="30"/>
-      <c r="U134" s="31"/>
+      <c r="D134" s="47"/>
+      <c r="E134" s="47"/>
+      <c r="F134" s="47"/>
+      <c r="G134" s="47"/>
+      <c r="H134" s="47"/>
+      <c r="I134" s="47"/>
+      <c r="J134" s="47"/>
+      <c r="K134" s="47"/>
+      <c r="L134" s="47"/>
+      <c r="M134" s="47"/>
+      <c r="N134" s="47"/>
+      <c r="O134" s="47"/>
+      <c r="P134" s="47"/>
+      <c r="Q134" s="47"/>
+      <c r="R134" s="47"/>
+      <c r="S134" s="47"/>
+      <c r="T134" s="47"/>
+      <c r="U134" s="48"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="34"/>
+      <c r="A135" s="37"/>
       <c r="B135" s="24" t="s">
         <v>182</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D135" s="30"/>
-      <c r="E135" s="30"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="30"/>
-      <c r="H135" s="30"/>
-      <c r="I135" s="30"/>
-      <c r="J135" s="30"/>
-      <c r="K135" s="30"/>
-      <c r="L135" s="30"/>
-      <c r="M135" s="30"/>
-      <c r="N135" s="30"/>
-      <c r="O135" s="30"/>
-      <c r="P135" s="30"/>
-      <c r="Q135" s="30"/>
-      <c r="R135" s="30"/>
-      <c r="S135" s="30"/>
-      <c r="T135" s="30"/>
-      <c r="U135" s="31"/>
+      <c r="D135" s="47"/>
+      <c r="E135" s="47"/>
+      <c r="F135" s="47"/>
+      <c r="G135" s="47"/>
+      <c r="H135" s="47"/>
+      <c r="I135" s="47"/>
+      <c r="J135" s="47"/>
+      <c r="K135" s="47"/>
+      <c r="L135" s="47"/>
+      <c r="M135" s="47"/>
+      <c r="N135" s="47"/>
+      <c r="O135" s="47"/>
+      <c r="P135" s="47"/>
+      <c r="Q135" s="47"/>
+      <c r="R135" s="47"/>
+      <c r="S135" s="47"/>
+      <c r="T135" s="47"/>
+      <c r="U135" s="48"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="34"/>
+      <c r="A136" s="37"/>
       <c r="B136" s="24" t="s">
         <v>183</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D136" s="32"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="32"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="32"/>
-      <c r="K136" s="32"/>
-      <c r="L136" s="32"/>
-      <c r="M136" s="32"/>
-      <c r="N136" s="32"/>
-      <c r="O136" s="32"/>
-      <c r="P136" s="32"/>
-      <c r="Q136" s="32"/>
-      <c r="R136" s="32"/>
-      <c r="S136" s="32"/>
-      <c r="T136" s="32"/>
-      <c r="U136" s="33"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="49"/>
+      <c r="F136" s="49"/>
+      <c r="G136" s="49"/>
+      <c r="H136" s="49"/>
+      <c r="I136" s="49"/>
+      <c r="J136" s="49"/>
+      <c r="K136" s="49"/>
+      <c r="L136" s="49"/>
+      <c r="M136" s="49"/>
+      <c r="N136" s="49"/>
+      <c r="O136" s="49"/>
+      <c r="P136" s="49"/>
+      <c r="Q136" s="49"/>
+      <c r="R136" s="49"/>
+      <c r="S136" s="49"/>
+      <c r="T136" s="49"/>
+      <c r="U136" s="50"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6595,6 +6595,26 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6611,26 +6631,6 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6673,81 +6673,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45" t="s">
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45" t="s">
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45" t="s">
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45" t="s">
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="46" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45" t="s">
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45" t="s">
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="34">
+      <c r="A4" s="37">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -6789,7 +6789,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="34"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -6849,7 +6849,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="34"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
@@ -6967,7 +6967,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="34"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="6" t="s">
         <v>37</v>
       </c>
@@ -7013,7 +7013,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="34"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="6" t="s">
         <v>39</v>
       </c>
@@ -7063,7 +7063,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="34"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
@@ -7107,7 +7107,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="35">
+      <c r="A11" s="38">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -7157,7 +7157,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="35"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="11" t="s">
         <v>50</v>
       </c>
@@ -7215,7 +7215,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="35"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="11" t="s">
         <v>51</v>
       </c>
@@ -7285,7 +7285,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="35"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="11" t="s">
         <v>55</v>
       </c>
@@ -7333,7 +7333,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="35"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="11" t="s">
         <v>56</v>
       </c>
@@ -7362,7 +7362,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="35"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="11" t="s">
         <v>57</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="35"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="11" t="s">
         <v>58</v>
       </c>
@@ -7424,7 +7424,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="37">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -7457,7 +7457,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="34"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
@@ -7500,7 +7500,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="34"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
@@ -7555,7 +7555,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="34"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -7598,7 +7598,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="34"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
@@ -7627,7 +7627,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="34"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
@@ -7654,7 +7654,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="34"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="15" t="s">
         <v>65</v>
       </c>
@@ -7681,7 +7681,7 @@
       <c r="U24" s="18"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="38">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -7714,7 +7714,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="35"/>
+      <c r="A26" s="38"/>
       <c r="B26" s="11" t="s">
         <v>67</v>
       </c>
@@ -7757,7 +7757,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="35"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="11" t="s">
         <v>68</v>
       </c>
@@ -7812,7 +7812,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="35"/>
+      <c r="A28" s="38"/>
       <c r="B28" s="11" t="s">
         <v>69</v>
       </c>
@@ -7855,90 +7855,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="35"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="37"/>
-      <c r="T29" s="37"/>
-      <c r="U29" s="38"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="30"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="35"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="19" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="40"/>
-      <c r="S30" s="40"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="41"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="33"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="35"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="44"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="34">
+      <c r="A32" s="37">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -7971,7 +7971,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="34"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="6" t="s">
         <v>75</v>
       </c>
@@ -8014,7 +8014,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="34"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="6" t="s">
         <v>76</v>
       </c>
@@ -8057,117 +8057,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="34"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-      <c r="T35" s="37"/>
-      <c r="U35" s="38"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="30"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="34"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="41"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="33"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="34"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="21" t="s">
         <v>79</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="40"/>
-      <c r="S37" s="40"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="41"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="33"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="34"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="21" t="s">
         <v>80</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="40"/>
-      <c r="S38" s="40"/>
-      <c r="T38" s="40"/>
-      <c r="U38" s="41"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="33"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="35">
+      <c r="A39" s="38">
         <v>6</v>
       </c>
       <c r="B39" s="21" t="s">
@@ -8176,81 +8176,81 @@
       <c r="C39" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="40"/>
-      <c r="S39" s="40"/>
-      <c r="T39" s="40"/>
-      <c r="U39" s="41"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="33"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="35"/>
+      <c r="A40" s="38"/>
       <c r="B40" s="21" t="s">
         <v>82</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="41"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="33"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="35"/>
+      <c r="A41" s="38"/>
       <c r="B41" s="21" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="44"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="36"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="35"/>
+      <c r="A42" s="38"/>
       <c r="B42" s="22" t="s">
         <v>84</v>
       </c>
@@ -8293,7 +8293,7 @@
       <c r="U42" s="14"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="35"/>
+      <c r="A43" s="38"/>
       <c r="B43" s="22" t="s">
         <v>85</v>
       </c>
@@ -8334,7 +8334,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="35"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="23" t="s">
         <v>86</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="U44" s="18"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="35"/>
+      <c r="A45" s="38"/>
       <c r="B45" s="22" t="s">
         <v>87</v>
       </c>
@@ -8388,7 +8388,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="34">
+      <c r="A46" s="37">
         <v>7</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -8433,7 +8433,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="34"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="24" t="s">
         <v>89</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="34"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="24" t="s">
         <v>90</v>
       </c>
@@ -8519,7 +8519,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="34"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="24" t="s">
         <v>91</v>
       </c>
@@ -8562,7 +8562,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="34"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="24" t="s">
         <v>93</v>
       </c>
@@ -8603,7 +8603,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="34"/>
+      <c r="A51" s="37"/>
       <c r="B51" s="24" t="s">
         <v>95</v>
       </c>
@@ -8638,7 +8638,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="34"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="24" t="s">
         <v>96</v>
       </c>
@@ -8665,7 +8665,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="35">
+      <c r="A53" s="38">
         <v>8</v>
       </c>
       <c r="B53" s="22" t="s">
@@ -8710,7 +8710,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="35"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="22" t="s">
         <v>98</v>
       </c>
@@ -8753,7 +8753,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="35"/>
+      <c r="A55" s="38"/>
       <c r="B55" s="22" t="s">
         <v>99</v>
       </c>
@@ -8808,7 +8808,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="35"/>
+      <c r="A56" s="38"/>
       <c r="B56" s="22" t="s">
         <v>100</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="U56" s="14"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="35"/>
+      <c r="A57" s="38"/>
       <c r="B57" s="22" t="s">
         <v>101</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="35"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="22" t="s">
         <v>102</v>
       </c>
@@ -8929,7 +8929,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="35"/>
+      <c r="A59" s="38"/>
       <c r="B59" s="22" t="s">
         <v>103</v>
       </c>
@@ -8956,7 +8956,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="34">
+      <c r="A60" s="37">
         <v>9</v>
       </c>
       <c r="B60" s="24" t="s">
@@ -9001,7 +9001,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="34"/>
+      <c r="A61" s="37"/>
       <c r="B61" s="24" t="s">
         <v>105</v>
       </c>
@@ -9044,7 +9044,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="34"/>
+      <c r="A62" s="37"/>
       <c r="B62" s="24" t="s">
         <v>106</v>
       </c>
@@ -9099,7 +9099,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="34"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="24" t="s">
         <v>107</v>
       </c>
@@ -9142,7 +9142,7 @@
       <c r="U63" s="25"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="34"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="24" t="s">
         <v>108</v>
       </c>
@@ -9185,7 +9185,7 @@
       <c r="U64" s="25"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="34"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="24" t="s">
         <v>109</v>
       </c>
@@ -9220,7 +9220,7 @@
       <c r="U65" s="25"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="34"/>
+      <c r="A66" s="37"/>
       <c r="B66" s="24" t="s">
         <v>110</v>
       </c>
@@ -9247,7 +9247,7 @@
       <c r="U66" s="25"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="35">
+      <c r="A67" s="38">
         <v>10</v>
       </c>
       <c r="B67" s="22" t="s">
@@ -9292,7 +9292,7 @@
       <c r="U67" s="26"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="35"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="22" t="s">
         <v>112</v>
       </c>
@@ -9335,7 +9335,7 @@
       <c r="U68" s="26"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="35"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="22" t="s">
         <v>113</v>
       </c>
@@ -9378,7 +9378,7 @@
       <c r="U69" s="26"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="35"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="22" t="s">
         <v>114</v>
       </c>
@@ -9421,7 +9421,7 @@
       <c r="U70" s="26"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="35"/>
+      <c r="A71" s="38"/>
       <c r="B71" s="22" t="s">
         <v>115</v>
       </c>
@@ -9464,7 +9464,7 @@
       <c r="U71" s="26"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="35"/>
+      <c r="A72" s="38"/>
       <c r="B72" s="22" t="s">
         <v>116</v>
       </c>
@@ -9491,7 +9491,7 @@
       <c r="U72" s="26"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="35"/>
+      <c r="A73" s="38"/>
       <c r="B73" s="22" t="s">
         <v>117</v>
       </c>
@@ -9518,7 +9518,7 @@
       <c r="U73" s="26"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="34">
+      <c r="A74" s="37">
         <v>11</v>
       </c>
       <c r="B74" s="24" t="s">
@@ -9563,7 +9563,7 @@
       <c r="U74" s="25"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="34"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="24" t="s">
         <v>119</v>
       </c>
@@ -9606,7 +9606,7 @@
       <c r="U75" s="25"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="34"/>
+      <c r="A76" s="37"/>
       <c r="B76" s="24" t="s">
         <v>120</v>
       </c>
@@ -9661,7 +9661,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="34"/>
+      <c r="A77" s="37"/>
       <c r="B77" s="24" t="s">
         <v>121</v>
       </c>
@@ -9704,7 +9704,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="34"/>
+      <c r="A78" s="37"/>
       <c r="B78" s="24" t="s">
         <v>122</v>
       </c>
@@ -9747,7 +9747,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="34"/>
+      <c r="A79" s="37"/>
       <c r="B79" s="24" t="s">
         <v>123</v>
       </c>
@@ -9774,7 +9774,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="34"/>
+      <c r="A80" s="37"/>
       <c r="B80" s="24" t="s">
         <v>124</v>
       </c>
@@ -9801,7 +9801,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="35">
+      <c r="A81" s="38">
         <v>12</v>
       </c>
       <c r="B81" s="22" t="s">
@@ -9846,7 +9846,7 @@
       <c r="U81" s="14"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="35"/>
+      <c r="A82" s="38"/>
       <c r="B82" s="22" t="s">
         <v>126</v>
       </c>
@@ -9889,7 +9889,7 @@
       <c r="U82" s="14"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="35"/>
+      <c r="A83" s="38"/>
       <c r="B83" s="22" t="s">
         <v>127</v>
       </c>
@@ -9944,7 +9944,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="35"/>
+      <c r="A84" s="38"/>
       <c r="B84" s="22" t="s">
         <v>130</v>
       </c>
@@ -9987,7 +9987,7 @@
       <c r="U84" s="14"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="35"/>
+      <c r="A85" s="38"/>
       <c r="B85" s="22" t="s">
         <v>131</v>
       </c>
@@ -10030,7 +10030,7 @@
       <c r="U85" s="14"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="35"/>
+      <c r="A86" s="38"/>
       <c r="B86" s="22" t="s">
         <v>132</v>
       </c>
@@ -10065,7 +10065,7 @@
       <c r="U86" s="14"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="35"/>
+      <c r="A87" s="38"/>
       <c r="B87" s="22" t="s">
         <v>133</v>
       </c>
@@ -10092,7 +10092,7 @@
       <c r="U87" s="14"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="34">
+      <c r="A88" s="37">
         <v>13</v>
       </c>
       <c r="B88" s="24" t="s">
@@ -10137,7 +10137,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="34"/>
+      <c r="A89" s="37"/>
       <c r="B89" s="24" t="s">
         <v>135</v>
       </c>
@@ -10180,7 +10180,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="34"/>
+      <c r="A90" s="37"/>
       <c r="B90" s="24" t="s">
         <v>136</v>
       </c>
@@ -10235,7 +10235,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="34"/>
+      <c r="A91" s="37"/>
       <c r="B91" s="24" t="s">
         <v>137</v>
       </c>
@@ -10278,7 +10278,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="34"/>
+      <c r="A92" s="37"/>
       <c r="B92" s="24" t="s">
         <v>138</v>
       </c>
@@ -10321,7 +10321,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="34"/>
+      <c r="A93" s="37"/>
       <c r="B93" s="24" t="s">
         <v>139</v>
       </c>
@@ -10356,7 +10356,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="34"/>
+      <c r="A94" s="37"/>
       <c r="B94" s="24" t="s">
         <v>140</v>
       </c>
@@ -10383,7 +10383,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="35">
+      <c r="A95" s="38">
         <v>14</v>
       </c>
       <c r="B95" s="22" t="s">
@@ -10428,7 +10428,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="35"/>
+      <c r="A96" s="38"/>
       <c r="B96" s="22" t="s">
         <v>142</v>
       </c>
@@ -10471,7 +10471,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="35"/>
+      <c r="A97" s="38"/>
       <c r="B97" s="22" t="s">
         <v>143</v>
       </c>
@@ -10526,7 +10526,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="35"/>
+      <c r="A98" s="38"/>
       <c r="B98" s="22" t="s">
         <v>144</v>
       </c>
@@ -10569,7 +10569,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="35"/>
+      <c r="A99" s="38"/>
       <c r="B99" s="22" t="s">
         <v>145</v>
       </c>
@@ -10612,7 +10612,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="35"/>
+      <c r="A100" s="38"/>
       <c r="B100" s="22" t="s">
         <v>146</v>
       </c>
@@ -10639,7 +10639,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="35"/>
+      <c r="A101" s="38"/>
       <c r="B101" s="22" t="s">
         <v>147</v>
       </c>
@@ -10666,7 +10666,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="34">
+      <c r="A102" s="37">
         <v>15</v>
       </c>
       <c r="B102" s="24" t="s">
@@ -10711,7 +10711,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="34"/>
+      <c r="A103" s="37"/>
       <c r="B103" s="24" t="s">
         <v>149</v>
       </c>
@@ -10754,7 +10754,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="34"/>
+      <c r="A104" s="37"/>
       <c r="B104" s="24" t="s">
         <v>150</v>
       </c>
@@ -10809,7 +10809,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="34"/>
+      <c r="A105" s="37"/>
       <c r="B105" s="24" t="s">
         <v>151</v>
       </c>
@@ -10852,7 +10852,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="34"/>
+      <c r="A106" s="37"/>
       <c r="B106" s="24" t="s">
         <v>152</v>
       </c>
@@ -10895,7 +10895,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="34"/>
+      <c r="A107" s="37"/>
       <c r="B107" s="24" t="s">
         <v>153</v>
       </c>
@@ -10930,7 +10930,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="34"/>
+      <c r="A108" s="37"/>
       <c r="B108" s="24" t="s">
         <v>154</v>
       </c>
@@ -10957,7 +10957,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="35">
+      <c r="A109" s="38">
         <v>16</v>
       </c>
       <c r="B109" s="22" t="s">
@@ -11002,7 +11002,7 @@
       <c r="U109" s="26"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="35"/>
+      <c r="A110" s="38"/>
       <c r="B110" s="22" t="s">
         <v>156</v>
       </c>
@@ -11045,7 +11045,7 @@
       <c r="U110" s="26"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="35"/>
+      <c r="A111" s="38"/>
       <c r="B111" s="22" t="s">
         <v>157</v>
       </c>
@@ -11100,7 +11100,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="35"/>
+      <c r="A112" s="38"/>
       <c r="B112" s="22" t="s">
         <v>158</v>
       </c>
@@ -11143,7 +11143,7 @@
       <c r="U112" s="26"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="35"/>
+      <c r="A113" s="38"/>
       <c r="B113" s="22" t="s">
         <v>159</v>
       </c>
@@ -11186,7 +11186,7 @@
       <c r="U113" s="26"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="35"/>
+      <c r="A114" s="38"/>
       <c r="B114" s="22" t="s">
         <v>160</v>
       </c>
@@ -11213,7 +11213,7 @@
       <c r="U114" s="26"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="35"/>
+      <c r="A115" s="38"/>
       <c r="B115" s="22" t="s">
         <v>161</v>
       </c>
@@ -11240,7 +11240,7 @@
       <c r="U115" s="26"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="34">
+      <c r="A116" s="37">
         <v>17</v>
       </c>
       <c r="B116" s="24" t="s">
@@ -11283,7 +11283,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="34"/>
+      <c r="A117" s="37"/>
       <c r="B117" s="24" t="s">
         <v>163</v>
       </c>
@@ -11324,7 +11324,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="34"/>
+      <c r="A118" s="37"/>
       <c r="B118" s="24" t="s">
         <v>164</v>
       </c>
@@ -11365,7 +11365,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="34"/>
+      <c r="A119" s="37"/>
       <c r="B119" s="24" t="s">
         <v>165</v>
       </c>
@@ -11406,7 +11406,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="34"/>
+      <c r="A120" s="37"/>
       <c r="B120" s="24" t="s">
         <v>166</v>
       </c>
@@ -11449,7 +11449,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="34"/>
+      <c r="A121" s="37"/>
       <c r="B121" s="24" t="s">
         <v>167</v>
       </c>
@@ -11476,7 +11476,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="34"/>
+      <c r="A122" s="37"/>
       <c r="B122" s="24" t="s">
         <v>168</v>
       </c>
@@ -11503,7 +11503,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="35">
+      <c r="A123" s="38">
         <v>18</v>
       </c>
       <c r="B123" s="22" t="s">
@@ -11512,191 +11512,191 @@
       <c r="C123" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="27" t="s">
+      <c r="D123" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="E123" s="28"/>
-      <c r="F123" s="28"/>
-      <c r="G123" s="28"/>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28"/>
-      <c r="J123" s="28"/>
-      <c r="K123" s="28"/>
-      <c r="L123" s="28"/>
-      <c r="M123" s="28"/>
-      <c r="N123" s="28"/>
-      <c r="O123" s="28"/>
-      <c r="P123" s="28"/>
-      <c r="Q123" s="28"/>
-      <c r="R123" s="28"/>
-      <c r="S123" s="28"/>
-      <c r="T123" s="28"/>
-      <c r="U123" s="29"/>
+      <c r="E123" s="45"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="45"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="45"/>
+      <c r="J123" s="45"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="45"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="45"/>
+      <c r="O123" s="45"/>
+      <c r="P123" s="45"/>
+      <c r="Q123" s="45"/>
+      <c r="R123" s="45"/>
+      <c r="S123" s="45"/>
+      <c r="T123" s="45"/>
+      <c r="U123" s="46"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="35"/>
+      <c r="A124" s="38"/>
       <c r="B124" s="22" t="s">
         <v>171</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="30"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="30"/>
-      <c r="H124" s="30"/>
-      <c r="I124" s="30"/>
-      <c r="J124" s="30"/>
-      <c r="K124" s="30"/>
-      <c r="L124" s="30"/>
-      <c r="M124" s="30"/>
-      <c r="N124" s="30"/>
-      <c r="O124" s="30"/>
-      <c r="P124" s="30"/>
-      <c r="Q124" s="30"/>
-      <c r="R124" s="30"/>
-      <c r="S124" s="30"/>
-      <c r="T124" s="30"/>
-      <c r="U124" s="31"/>
+      <c r="D124" s="47"/>
+      <c r="E124" s="47"/>
+      <c r="F124" s="47"/>
+      <c r="G124" s="47"/>
+      <c r="H124" s="47"/>
+      <c r="I124" s="47"/>
+      <c r="J124" s="47"/>
+      <c r="K124" s="47"/>
+      <c r="L124" s="47"/>
+      <c r="M124" s="47"/>
+      <c r="N124" s="47"/>
+      <c r="O124" s="47"/>
+      <c r="P124" s="47"/>
+      <c r="Q124" s="47"/>
+      <c r="R124" s="47"/>
+      <c r="S124" s="47"/>
+      <c r="T124" s="47"/>
+      <c r="U124" s="48"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="35"/>
+      <c r="A125" s="38"/>
       <c r="B125" s="22" t="s">
         <v>172</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D125" s="30"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="30"/>
-      <c r="H125" s="30"/>
-      <c r="I125" s="30"/>
-      <c r="J125" s="30"/>
-      <c r="K125" s="30"/>
-      <c r="L125" s="30"/>
-      <c r="M125" s="30"/>
-      <c r="N125" s="30"/>
-      <c r="O125" s="30"/>
-      <c r="P125" s="30"/>
-      <c r="Q125" s="30"/>
-      <c r="R125" s="30"/>
-      <c r="S125" s="30"/>
-      <c r="T125" s="30"/>
-      <c r="U125" s="31"/>
+      <c r="D125" s="47"/>
+      <c r="E125" s="47"/>
+      <c r="F125" s="47"/>
+      <c r="G125" s="47"/>
+      <c r="H125" s="47"/>
+      <c r="I125" s="47"/>
+      <c r="J125" s="47"/>
+      <c r="K125" s="47"/>
+      <c r="L125" s="47"/>
+      <c r="M125" s="47"/>
+      <c r="N125" s="47"/>
+      <c r="O125" s="47"/>
+      <c r="P125" s="47"/>
+      <c r="Q125" s="47"/>
+      <c r="R125" s="47"/>
+      <c r="S125" s="47"/>
+      <c r="T125" s="47"/>
+      <c r="U125" s="48"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="35"/>
+      <c r="A126" s="38"/>
       <c r="B126" s="22" t="s">
         <v>173</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D126" s="30"/>
-      <c r="E126" s="30"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="30"/>
-      <c r="H126" s="30"/>
-      <c r="I126" s="30"/>
-      <c r="J126" s="30"/>
-      <c r="K126" s="30"/>
-      <c r="L126" s="30"/>
-      <c r="M126" s="30"/>
-      <c r="N126" s="30"/>
-      <c r="O126" s="30"/>
-      <c r="P126" s="30"/>
-      <c r="Q126" s="30"/>
-      <c r="R126" s="30"/>
-      <c r="S126" s="30"/>
-      <c r="T126" s="30"/>
-      <c r="U126" s="31"/>
+      <c r="D126" s="47"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="47"/>
+      <c r="G126" s="47"/>
+      <c r="H126" s="47"/>
+      <c r="I126" s="47"/>
+      <c r="J126" s="47"/>
+      <c r="K126" s="47"/>
+      <c r="L126" s="47"/>
+      <c r="M126" s="47"/>
+      <c r="N126" s="47"/>
+      <c r="O126" s="47"/>
+      <c r="P126" s="47"/>
+      <c r="Q126" s="47"/>
+      <c r="R126" s="47"/>
+      <c r="S126" s="47"/>
+      <c r="T126" s="47"/>
+      <c r="U126" s="48"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="35"/>
+      <c r="A127" s="38"/>
       <c r="B127" s="21" t="s">
         <v>174</v>
       </c>
       <c r="C127" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="30"/>
-      <c r="E127" s="30"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="30"/>
-      <c r="H127" s="30"/>
-      <c r="I127" s="30"/>
-      <c r="J127" s="30"/>
-      <c r="K127" s="30"/>
-      <c r="L127" s="30"/>
-      <c r="M127" s="30"/>
-      <c r="N127" s="30"/>
-      <c r="O127" s="30"/>
-      <c r="P127" s="30"/>
-      <c r="Q127" s="30"/>
-      <c r="R127" s="30"/>
-      <c r="S127" s="30"/>
-      <c r="T127" s="30"/>
-      <c r="U127" s="31"/>
+      <c r="D127" s="47"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="47"/>
+      <c r="G127" s="47"/>
+      <c r="H127" s="47"/>
+      <c r="I127" s="47"/>
+      <c r="J127" s="47"/>
+      <c r="K127" s="47"/>
+      <c r="L127" s="47"/>
+      <c r="M127" s="47"/>
+      <c r="N127" s="47"/>
+      <c r="O127" s="47"/>
+      <c r="P127" s="47"/>
+      <c r="Q127" s="47"/>
+      <c r="R127" s="47"/>
+      <c r="S127" s="47"/>
+      <c r="T127" s="47"/>
+      <c r="U127" s="48"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="35"/>
+      <c r="A128" s="38"/>
       <c r="B128" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="30"/>
-      <c r="H128" s="30"/>
-      <c r="I128" s="30"/>
-      <c r="J128" s="30"/>
-      <c r="K128" s="30"/>
-      <c r="L128" s="30"/>
-      <c r="M128" s="30"/>
-      <c r="N128" s="30"/>
-      <c r="O128" s="30"/>
-      <c r="P128" s="30"/>
-      <c r="Q128" s="30"/>
-      <c r="R128" s="30"/>
-      <c r="S128" s="30"/>
-      <c r="T128" s="30"/>
-      <c r="U128" s="31"/>
+      <c r="D128" s="47"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="47"/>
+      <c r="G128" s="47"/>
+      <c r="H128" s="47"/>
+      <c r="I128" s="47"/>
+      <c r="J128" s="47"/>
+      <c r="K128" s="47"/>
+      <c r="L128" s="47"/>
+      <c r="M128" s="47"/>
+      <c r="N128" s="47"/>
+      <c r="O128" s="47"/>
+      <c r="P128" s="47"/>
+      <c r="Q128" s="47"/>
+      <c r="R128" s="47"/>
+      <c r="S128" s="47"/>
+      <c r="T128" s="47"/>
+      <c r="U128" s="48"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="35"/>
+      <c r="A129" s="38"/>
       <c r="B129" s="22" t="s">
         <v>176</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D129" s="30"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="30"/>
-      <c r="H129" s="30"/>
-      <c r="I129" s="30"/>
-      <c r="J129" s="30"/>
-      <c r="K129" s="30"/>
-      <c r="L129" s="30"/>
-      <c r="M129" s="30"/>
-      <c r="N129" s="30"/>
-      <c r="O129" s="30"/>
-      <c r="P129" s="30"/>
-      <c r="Q129" s="30"/>
-      <c r="R129" s="30"/>
-      <c r="S129" s="30"/>
-      <c r="T129" s="30"/>
-      <c r="U129" s="31"/>
+      <c r="D129" s="47"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="47"/>
+      <c r="G129" s="47"/>
+      <c r="H129" s="47"/>
+      <c r="I129" s="47"/>
+      <c r="J129" s="47"/>
+      <c r="K129" s="47"/>
+      <c r="L129" s="47"/>
+      <c r="M129" s="47"/>
+      <c r="N129" s="47"/>
+      <c r="O129" s="47"/>
+      <c r="P129" s="47"/>
+      <c r="Q129" s="47"/>
+      <c r="R129" s="47"/>
+      <c r="S129" s="47"/>
+      <c r="T129" s="47"/>
+      <c r="U129" s="48"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="34">
+      <c r="A130" s="37">
         <v>19</v>
       </c>
       <c r="B130" s="24" t="s">
@@ -11705,186 +11705,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="30"/>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="30"/>
-      <c r="H130" s="30"/>
-      <c r="I130" s="30"/>
-      <c r="J130" s="30"/>
-      <c r="K130" s="30"/>
-      <c r="L130" s="30"/>
-      <c r="M130" s="30"/>
-      <c r="N130" s="30"/>
-      <c r="O130" s="30"/>
-      <c r="P130" s="30"/>
-      <c r="Q130" s="30"/>
-      <c r="R130" s="30"/>
-      <c r="S130" s="30"/>
-      <c r="T130" s="30"/>
-      <c r="U130" s="31"/>
+      <c r="D130" s="47"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="47"/>
+      <c r="G130" s="47"/>
+      <c r="H130" s="47"/>
+      <c r="I130" s="47"/>
+      <c r="J130" s="47"/>
+      <c r="K130" s="47"/>
+      <c r="L130" s="47"/>
+      <c r="M130" s="47"/>
+      <c r="N130" s="47"/>
+      <c r="O130" s="47"/>
+      <c r="P130" s="47"/>
+      <c r="Q130" s="47"/>
+      <c r="R130" s="47"/>
+      <c r="S130" s="47"/>
+      <c r="T130" s="47"/>
+      <c r="U130" s="48"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="34"/>
+      <c r="A131" s="37"/>
       <c r="B131" s="24" t="s">
         <v>178</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="30"/>
-      <c r="E131" s="30"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="30"/>
-      <c r="H131" s="30"/>
-      <c r="I131" s="30"/>
-      <c r="J131" s="30"/>
-      <c r="K131" s="30"/>
-      <c r="L131" s="30"/>
-      <c r="M131" s="30"/>
-      <c r="N131" s="30"/>
-      <c r="O131" s="30"/>
-      <c r="P131" s="30"/>
-      <c r="Q131" s="30"/>
-      <c r="R131" s="30"/>
-      <c r="S131" s="30"/>
-      <c r="T131" s="30"/>
-      <c r="U131" s="31"/>
+      <c r="D131" s="47"/>
+      <c r="E131" s="47"/>
+      <c r="F131" s="47"/>
+      <c r="G131" s="47"/>
+      <c r="H131" s="47"/>
+      <c r="I131" s="47"/>
+      <c r="J131" s="47"/>
+      <c r="K131" s="47"/>
+      <c r="L131" s="47"/>
+      <c r="M131" s="47"/>
+      <c r="N131" s="47"/>
+      <c r="O131" s="47"/>
+      <c r="P131" s="47"/>
+      <c r="Q131" s="47"/>
+      <c r="R131" s="47"/>
+      <c r="S131" s="47"/>
+      <c r="T131" s="47"/>
+      <c r="U131" s="48"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="34"/>
+      <c r="A132" s="37"/>
       <c r="B132" s="24" t="s">
         <v>179</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D132" s="30"/>
-      <c r="E132" s="30"/>
-      <c r="F132" s="30"/>
-      <c r="G132" s="30"/>
-      <c r="H132" s="30"/>
-      <c r="I132" s="30"/>
-      <c r="J132" s="30"/>
-      <c r="K132" s="30"/>
-      <c r="L132" s="30"/>
-      <c r="M132" s="30"/>
-      <c r="N132" s="30"/>
-      <c r="O132" s="30"/>
-      <c r="P132" s="30"/>
-      <c r="Q132" s="30"/>
-      <c r="R132" s="30"/>
-      <c r="S132" s="30"/>
-      <c r="T132" s="30"/>
-      <c r="U132" s="31"/>
+      <c r="D132" s="47"/>
+      <c r="E132" s="47"/>
+      <c r="F132" s="47"/>
+      <c r="G132" s="47"/>
+      <c r="H132" s="47"/>
+      <c r="I132" s="47"/>
+      <c r="J132" s="47"/>
+      <c r="K132" s="47"/>
+      <c r="L132" s="47"/>
+      <c r="M132" s="47"/>
+      <c r="N132" s="47"/>
+      <c r="O132" s="47"/>
+      <c r="P132" s="47"/>
+      <c r="Q132" s="47"/>
+      <c r="R132" s="47"/>
+      <c r="S132" s="47"/>
+      <c r="T132" s="47"/>
+      <c r="U132" s="48"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="34"/>
+      <c r="A133" s="37"/>
       <c r="B133" s="24" t="s">
         <v>180</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D133" s="30"/>
-      <c r="E133" s="30"/>
-      <c r="F133" s="30"/>
-      <c r="G133" s="30"/>
-      <c r="H133" s="30"/>
-      <c r="I133" s="30"/>
-      <c r="J133" s="30"/>
-      <c r="K133" s="30"/>
-      <c r="L133" s="30"/>
-      <c r="M133" s="30"/>
-      <c r="N133" s="30"/>
-      <c r="O133" s="30"/>
-      <c r="P133" s="30"/>
-      <c r="Q133" s="30"/>
-      <c r="R133" s="30"/>
-      <c r="S133" s="30"/>
-      <c r="T133" s="30"/>
-      <c r="U133" s="31"/>
+      <c r="D133" s="47"/>
+      <c r="E133" s="47"/>
+      <c r="F133" s="47"/>
+      <c r="G133" s="47"/>
+      <c r="H133" s="47"/>
+      <c r="I133" s="47"/>
+      <c r="J133" s="47"/>
+      <c r="K133" s="47"/>
+      <c r="L133" s="47"/>
+      <c r="M133" s="47"/>
+      <c r="N133" s="47"/>
+      <c r="O133" s="47"/>
+      <c r="P133" s="47"/>
+      <c r="Q133" s="47"/>
+      <c r="R133" s="47"/>
+      <c r="S133" s="47"/>
+      <c r="T133" s="47"/>
+      <c r="U133" s="48"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="34"/>
+      <c r="A134" s="37"/>
       <c r="B134" s="24" t="s">
         <v>181</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="30"/>
-      <c r="E134" s="30"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="30"/>
-      <c r="H134" s="30"/>
-      <c r="I134" s="30"/>
-      <c r="J134" s="30"/>
-      <c r="K134" s="30"/>
-      <c r="L134" s="30"/>
-      <c r="M134" s="30"/>
-      <c r="N134" s="30"/>
-      <c r="O134" s="30"/>
-      <c r="P134" s="30"/>
-      <c r="Q134" s="30"/>
-      <c r="R134" s="30"/>
-      <c r="S134" s="30"/>
-      <c r="T134" s="30"/>
-      <c r="U134" s="31"/>
+      <c r="D134" s="47"/>
+      <c r="E134" s="47"/>
+      <c r="F134" s="47"/>
+      <c r="G134" s="47"/>
+      <c r="H134" s="47"/>
+      <c r="I134" s="47"/>
+      <c r="J134" s="47"/>
+      <c r="K134" s="47"/>
+      <c r="L134" s="47"/>
+      <c r="M134" s="47"/>
+      <c r="N134" s="47"/>
+      <c r="O134" s="47"/>
+      <c r="P134" s="47"/>
+      <c r="Q134" s="47"/>
+      <c r="R134" s="47"/>
+      <c r="S134" s="47"/>
+      <c r="T134" s="47"/>
+      <c r="U134" s="48"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="34"/>
+      <c r="A135" s="37"/>
       <c r="B135" s="24" t="s">
         <v>182</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D135" s="30"/>
-      <c r="E135" s="30"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="30"/>
-      <c r="H135" s="30"/>
-      <c r="I135" s="30"/>
-      <c r="J135" s="30"/>
-      <c r="K135" s="30"/>
-      <c r="L135" s="30"/>
-      <c r="M135" s="30"/>
-      <c r="N135" s="30"/>
-      <c r="O135" s="30"/>
-      <c r="P135" s="30"/>
-      <c r="Q135" s="30"/>
-      <c r="R135" s="30"/>
-      <c r="S135" s="30"/>
-      <c r="T135" s="30"/>
-      <c r="U135" s="31"/>
+      <c r="D135" s="47"/>
+      <c r="E135" s="47"/>
+      <c r="F135" s="47"/>
+      <c r="G135" s="47"/>
+      <c r="H135" s="47"/>
+      <c r="I135" s="47"/>
+      <c r="J135" s="47"/>
+      <c r="K135" s="47"/>
+      <c r="L135" s="47"/>
+      <c r="M135" s="47"/>
+      <c r="N135" s="47"/>
+      <c r="O135" s="47"/>
+      <c r="P135" s="47"/>
+      <c r="Q135" s="47"/>
+      <c r="R135" s="47"/>
+      <c r="S135" s="47"/>
+      <c r="T135" s="47"/>
+      <c r="U135" s="48"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="34"/>
+      <c r="A136" s="37"/>
       <c r="B136" s="24" t="s">
         <v>183</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D136" s="32"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="32"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="32"/>
-      <c r="K136" s="32"/>
-      <c r="L136" s="32"/>
-      <c r="M136" s="32"/>
-      <c r="N136" s="32"/>
-      <c r="O136" s="32"/>
-      <c r="P136" s="32"/>
-      <c r="Q136" s="32"/>
-      <c r="R136" s="32"/>
-      <c r="S136" s="32"/>
-      <c r="T136" s="32"/>
-      <c r="U136" s="33"/>
+      <c r="D136" s="49"/>
+      <c r="E136" s="49"/>
+      <c r="F136" s="49"/>
+      <c r="G136" s="49"/>
+      <c r="H136" s="49"/>
+      <c r="I136" s="49"/>
+      <c r="J136" s="49"/>
+      <c r="K136" s="49"/>
+      <c r="L136" s="49"/>
+      <c r="M136" s="49"/>
+      <c r="N136" s="49"/>
+      <c r="O136" s="49"/>
+      <c r="P136" s="49"/>
+      <c r="Q136" s="49"/>
+      <c r="R136" s="49"/>
+      <c r="S136" s="49"/>
+      <c r="T136" s="49"/>
+      <c r="U136" s="50"/>
     </row>
     <row r="137" spans="1:21" ht="13.9" customHeight="1"/>
     <row r="138" spans="1:21"/>
@@ -11902,6 +11902,26 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -11918,26 +11938,6 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
